--- a/query4_results.xlsx
+++ b/query4_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5285cb0be836e74d/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5285cb0be836e74d/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1E4809E9-3DE6-43FB-A5F0-841ADA499F26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C6249E79-0628-4992-8178-5A3722D67A9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2625" windowWidth="21600" windowHeight="11295" xr2:uid="{35BD3CFF-62E9-4C3A-933C-3F5B087F02CF}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{9AF5A049-1632-46FE-8C11-7DB3B4489B1F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,12 +31,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>field_size_category</t>
   </si>
@@ -47,10 +50,19 @@
     <t>avg_field_size</t>
   </si>
   <si>
+    <t>total_invested</t>
+  </si>
+  <si>
+    <t>total_winnings</t>
+  </si>
+  <si>
     <t>total_profit</t>
   </si>
   <si>
-    <t>avg_roi_pct</t>
+    <t>portfolio_roi_pct</t>
+  </si>
+  <si>
+    <t>avg_entry_roi_pct</t>
   </si>
   <si>
     <t>Head-to-Head (2-9)</t>
@@ -440,14 +452,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37902BA6-8823-44EE-AE1F-1CFBBFACEBFC}">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFFF1C83-9A6E-449C-8F00-808788CE1A44}">
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,10 +482,19 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2">
         <v>3531</v>
@@ -475,15 +503,24 @@
         <v>2</v>
       </c>
       <c r="D2" s="1">
+        <v>16557</v>
+      </c>
+      <c r="E2" s="1">
+        <v>19681.150000000001</v>
+      </c>
+      <c r="F2" s="1">
         <v>3124.15</v>
       </c>
-      <c r="E2">
+      <c r="G2">
+        <v>18.87</v>
+      </c>
+      <c r="H2">
         <v>1.81</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3">
         <v>2777</v>
@@ -492,15 +529,24 @@
         <v>37</v>
       </c>
       <c r="D3" s="1">
+        <v>17129.099999999999</v>
+      </c>
+      <c r="E3" s="1">
+        <v>20605.73</v>
+      </c>
+      <c r="F3" s="1">
         <v>3476.63</v>
       </c>
-      <c r="E3">
+      <c r="G3">
+        <v>20.3</v>
+      </c>
+      <c r="H3">
         <v>25.59</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4">
         <v>1899</v>
@@ -509,15 +555,24 @@
         <v>249</v>
       </c>
       <c r="D4" s="1">
+        <v>36652.5</v>
+      </c>
+      <c r="E4" s="1">
+        <v>43404.67</v>
+      </c>
+      <c r="F4" s="1">
         <v>6752.17</v>
       </c>
-      <c r="E4">
+      <c r="G4">
+        <v>18.420000000000002</v>
+      </c>
+      <c r="H4">
         <v>35.26</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5">
         <v>1986</v>
@@ -526,15 +581,24 @@
         <v>4776</v>
       </c>
       <c r="D5" s="1">
+        <v>36726</v>
+      </c>
+      <c r="E5" s="1">
+        <v>92207.95</v>
+      </c>
+      <c r="F5" s="1">
         <v>55481.95</v>
       </c>
-      <c r="E5">
+      <c r="G5">
+        <v>151.07</v>
+      </c>
+      <c r="H5">
         <v>13.65</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6">
         <v>18298</v>
@@ -543,9 +607,18 @@
         <v>66426</v>
       </c>
       <c r="D6" s="1">
+        <v>74328.289999999994</v>
+      </c>
+      <c r="E6" s="1">
+        <v>119306.98</v>
+      </c>
+      <c r="F6" s="1">
         <v>44978.69</v>
       </c>
-      <c r="E6">
+      <c r="G6">
+        <v>60.51</v>
+      </c>
+      <c r="H6">
         <v>57.1</v>
       </c>
     </row>
